--- a/1. Database Design/Java23 HuynhVuHoangNguyen Database Design.xlsx
+++ b/1. Database Design/Java23 HuynhVuHoangNguyen Database Design.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\work\java23\3. Database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\work\java23\3. Database\1. Database Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5E3206-C8EC-4915-B0C0-241775F1CDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59071ECB-B7EC-4156-8CA6-00A81F5E6E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4110" yWindow="4110" windowWidth="21600" windowHeight="11385" tabRatio="633" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="17775" windowHeight="11385" tabRatio="633" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="B1-Mô hình quan niệm" sheetId="5" r:id="rId1"/>
@@ -194,8 +194,173 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Vince</author>
+  </authors>
+  <commentList>
+    <comment ref="K6" authorId="0" shapeId="0" xr:uid="{088BCA39-2763-49B2-B8C7-2A2F2B251553}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Vince:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Khách
+Nhân Viên
+Quản Lý
+Giám Đốc</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L6" authorId="0" shapeId="0" xr:uid="{B67F5A9E-5BE4-4411-AB44-4982E3FE6830}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Vince:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Chờ xử lý
+Đã xử lý chờ đóng gói
+Đang đóng gói
+Đang giao hàng
+Giao hàng thành công
+Giao hàng thất bại</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N6" authorId="0" shapeId="0" xr:uid="{B4800CD9-A748-4395-8781-AA89F293C20D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Vince:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+COD
+Chuyển Khoảng
+Thẻ ghi nợ
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q7" authorId="0" shapeId="0" xr:uid="{760FCF6C-5194-44CE-A9DE-9D3119D2C69D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Vince:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Số lượng bán của mặt hàng trong đơn hàng</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P8" authorId="0" shapeId="0" xr:uid="{F09A8124-0B4D-432B-90F0-725F6CADF5AC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Vince:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Tìm những đơn hàng bị hủy</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{079C4AA2-C043-4BF7-B907-C7BCF05160D8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Vince:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Số lượng tồn kho</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="406">
   <si>
     <t>MatHang</t>
   </si>
@@ -1146,6 +1311,417 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1piESfuNSHgadUj1hfForCNigHCkfQL78/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>java23_shopping</t>
+  </si>
+  <si>
+    <t>N N</t>
+  </si>
+  <si>
+    <t>T01_ITEM</t>
+  </si>
+  <si>
+    <t>T02_SIZE</t>
+  </si>
+  <si>
+    <t>T03_ITEM_DETAIL</t>
+  </si>
+  <si>
+    <t>T04_ITEM_GROUP</t>
+  </si>
+  <si>
+    <t>T05_GALLERY</t>
+  </si>
+  <si>
+    <t>T06_ORDER</t>
+  </si>
+  <si>
+    <t>T07_CUSTOMER</t>
+  </si>
+  <si>
+    <t>T08_EMPLOYEE</t>
+  </si>
+  <si>
+    <t>T09_ACCOUNT</t>
+  </si>
+  <si>
+    <t>T10_ROLE</t>
+  </si>
+  <si>
+    <t>T11_ORDER_STATUS</t>
+  </si>
+  <si>
+    <t>T12_ORDER_STATUS_DETAIL</t>
+  </si>
+  <si>
+    <t>T13_PAYMENT_METHOD</t>
+  </si>
+  <si>
+    <t>T14_TITLE</t>
+  </si>
+  <si>
+    <t>T15_BILL</t>
+  </si>
+  <si>
+    <t>T16_ORDER_DETAILS</t>
+  </si>
+  <si>
+    <t>T17_ITEM_RECEIVED_NOTE</t>
+  </si>
+  <si>
+    <t>T18_ITEM_RECEIVED_NOTE_DETAIL</t>
+  </si>
+  <si>
+    <t>T19_PROVIDER</t>
+  </si>
+  <si>
+    <t>C01_ITEM_ID</t>
+  </si>
+  <si>
+    <t>C02_SIZE_ID</t>
+  </si>
+  <si>
+    <t>C03_ITEM_DETAIL_ID</t>
+  </si>
+  <si>
+    <t>C04_ITEM_GROUP_ID</t>
+  </si>
+  <si>
+    <t>C04_ITEM_ID</t>
+  </si>
+  <si>
+    <t>C06_ORDER_ID</t>
+  </si>
+  <si>
+    <t>C07_CUSTOMNER_ID</t>
+  </si>
+  <si>
+    <t>C08_EMPLOYEE_ID</t>
+  </si>
+  <si>
+    <t>C09_ACCOUNT_ID</t>
+  </si>
+  <si>
+    <t>C10_ROLE_ID</t>
+  </si>
+  <si>
+    <t>C11_ORDER_STATUS_ID</t>
+  </si>
+  <si>
+    <t>C012_ORDER_ID</t>
+  </si>
+  <si>
+    <t>C13_PAYMENT_METHOD_ID</t>
+  </si>
+  <si>
+    <t>C14_TITLE_ID</t>
+  </si>
+  <si>
+    <t>C15_BILL_ID</t>
+  </si>
+  <si>
+    <t>C16_ORDER_ID</t>
+  </si>
+  <si>
+    <t>C17_IRN_ID</t>
+  </si>
+  <si>
+    <t>C18_IRN_ID</t>
+  </si>
+  <si>
+    <t>C19_PROVIDER_ID</t>
+  </si>
+  <si>
+    <t>C01_ITEM_NAME</t>
+  </si>
+  <si>
+    <t>C02_SIZE_NAME</t>
+  </si>
+  <si>
+    <t>C03_ITEM_ID</t>
+  </si>
+  <si>
+    <t>C04_ITEM_GROUP_NAME</t>
+  </si>
+  <si>
+    <t>C05_COLOR</t>
+  </si>
+  <si>
+    <t>C06_RECEIVER_NAME</t>
+  </si>
+  <si>
+    <t>C07_CUSTOMER_NAME</t>
+  </si>
+  <si>
+    <t>C08_EMPLOYEE_NAME</t>
+  </si>
+  <si>
+    <t>C09_USERNAME</t>
+  </si>
+  <si>
+    <t>C10_ROLE_NAME</t>
+  </si>
+  <si>
+    <t>C11_ORDER_STATUS_DESC</t>
+  </si>
+  <si>
+    <t>C12_ORDER_STATUS_ID</t>
+  </si>
+  <si>
+    <t>C13_PAYMENT_METHOD_NAME</t>
+  </si>
+  <si>
+    <t>C14_TITLE_NAME</t>
+  </si>
+  <si>
+    <t>C15_DELIVERY_FEE</t>
+  </si>
+  <si>
+    <t>C16_ITEM_DETAIL_ID</t>
+  </si>
+  <si>
+    <t>C17_IRN_TIME</t>
+  </si>
+  <si>
+    <t>C18_ITEM_ID</t>
+  </si>
+  <si>
+    <t>C19_PROVIDER_NAME</t>
+  </si>
+  <si>
+    <t>C01_ITEM_GROUP_ID</t>
+  </si>
+  <si>
+    <t>C02_GENDER</t>
+  </si>
+  <si>
+    <t>C03_SIZE_ID</t>
+  </si>
+  <si>
+    <t>C04_IMAGE</t>
+  </si>
+  <si>
+    <t>C06_RECEIVER_PHONE</t>
+  </si>
+  <si>
+    <t>C07_CUSTOMNER_PHONE</t>
+  </si>
+  <si>
+    <t>C08_EMPLOYEE_PHONE</t>
+  </si>
+  <si>
+    <t>C09_PASSWORD</t>
+  </si>
+  <si>
+    <t>C12_EMPLOYEE_ID</t>
+  </si>
+  <si>
+    <t>C15_TOTAL_OF_MONEY</t>
+  </si>
+  <si>
+    <t>C16_AMOUNT</t>
+  </si>
+  <si>
+    <t>C17_EMPLOYEE_ID</t>
+  </si>
+  <si>
+    <t>C18_AMOUNT</t>
+  </si>
+  <si>
+    <t>C19_PROVIDER_TAX</t>
+  </si>
+  <si>
+    <t>C02_SIZE_DESC</t>
+  </si>
+  <si>
+    <t>C03_COLOR</t>
+  </si>
+  <si>
+    <t>C06_RECEIVER_ADDRESS</t>
+  </si>
+  <si>
+    <t>C07_CUSTOMNER_EMAIL</t>
+  </si>
+  <si>
+    <t>C08_EMPLOYEE_EMAIL</t>
+  </si>
+  <si>
+    <t>C09_ACCOUNT_STATUS</t>
+  </si>
+  <si>
+    <t>C12_LAST_UPDATED</t>
+  </si>
+  <si>
+    <t>C15_ORDER_ID</t>
+  </si>
+  <si>
+    <t>C18_BUY_PRICE</t>
+  </si>
+  <si>
+    <t>C03_SALE_PRICE</t>
+  </si>
+  <si>
+    <t>C06_CUSTOMNER_ID</t>
+  </si>
+  <si>
+    <t>C07_CUSTOMNER_GENDER</t>
+  </si>
+  <si>
+    <t>C08_EMPLOYEE_GENDER</t>
+  </si>
+  <si>
+    <t>C09_ROLE_ID</t>
+  </si>
+  <si>
+    <t>C03_AMOUNT</t>
+  </si>
+  <si>
+    <t>C06_ORDER_TIME</t>
+  </si>
+  <si>
+    <t>C07_CUSTOMNER_DOB</t>
+  </si>
+  <si>
+    <t>C08_EMPLOYEE_DOB</t>
+  </si>
+  <si>
+    <t>C06_PAYMENT_METHOD_ID</t>
+  </si>
+  <si>
+    <t>C07_CUSTOMNER_ADDRESS</t>
+  </si>
+  <si>
+    <t>C08_TITLE_ID</t>
+  </si>
+  <si>
+    <t>C06_EMPLOYEE_ID</t>
+  </si>
+  <si>
+    <t>C07_ACCOUNT_ID</t>
+  </si>
+  <si>
+    <t>C08_ACCOUNT_ID</t>
+  </si>
+  <si>
+    <t>Khóa chính có 2 column, được tham chiếu từ table khác</t>
+  </si>
+  <si>
+    <t>Bản tham chiếu sẽ cần có 2 columns này</t>
+  </si>
+  <si>
+    <t>Tạo một column mới làm khóa chính đại diện cho table</t>
+  </si>
+  <si>
+    <t>UNIQUE</t>
+  </si>
+  <si>
+    <t>Áo sơ mi</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Size S - Nữ - từ 40 đến 50kg</t>
+  </si>
+  <si>
+    <t>Quần jean</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>XXL</t>
+  </si>
+  <si>
+    <t>white</t>
+  </si>
+  <si>
+    <t>file://img01</t>
+  </si>
+  <si>
+    <t>Size S - Nam - từ 45 đến 55kg</t>
+  </si>
+  <si>
+    <t>1. Database</t>
+  </si>
+  <si>
+    <t>file://img03</t>
+  </si>
+  <si>
+    <t>2. Tables</t>
+  </si>
+  <si>
+    <t>black</t>
+  </si>
+  <si>
+    <t>file://img02</t>
+  </si>
+  <si>
+    <t>3. Columns</t>
+  </si>
+  <si>
+    <t>4. Constrains: Primary, Foreign Keys, Unique, NOT NULL, IN SET</t>
+  </si>
+  <si>
+    <t>… View, Function, Procedure, Index, Partition, Trigger</t>
+  </si>
+  <si>
+    <t>T03_ITEM_DETAIL kết hợp của ITEM và Size</t>
+  </si>
+  <si>
+    <t>C03_SIZE_NAME</t>
+  </si>
+  <si>
+    <t>C01_COLOR</t>
+  </si>
+  <si>
+    <t>Chờ xử lý</t>
+  </si>
+  <si>
+    <t>NV1</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t>Đang giao</t>
+  </si>
+  <si>
+    <t>NV2</t>
+  </si>
+  <si>
+    <t>NV4</t>
+  </si>
+  <si>
+    <t>NV6</t>
+  </si>
+  <si>
+    <t>Giao thành công</t>
+  </si>
+  <si>
+    <t>Các cách để tạo ra CSDL sau quá trình thiết kế</t>
+  </si>
+  <si>
+    <t>1. Sử dụng các lệnh, cú pháp của SQL code tay mọi thứ</t>
+  </si>
+  <si>
+    <t>Lưu ý: quản lý database creating theo version</t>
+  </si>
+  <si>
+    <t>2. Sử dụng các RDBMS tools ví dụ như mySQL workbench</t>
+  </si>
+  <si>
+    <t>Tạo ra các diagram, generate tạo ra code sql, lấy sql chạy lên ra database của mình</t>
+  </si>
+  <si>
+    <t>3. Sử dụng ngôn ngữ phía backend kết hợp database</t>
+  </si>
+  <si>
+    <t>Cấu hình trong Java Backend, start dự án cung cấp url đến RDBMS</t>
+  </si>
+  <si>
+    <t>Tạo ra database</t>
   </si>
 </sst>
 </file>
@@ -1190,23 +1766,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FFFFC000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1279,8 +1839,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1347,6 +1922,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1394,9 +1975,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1427,18 +2008,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1471,26 +2040,26 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1514,8 +2083,8 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1524,14 +2093,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1553,13 +2135,37 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1588,8 +2194,8 @@
       <xdr:rowOff>70090</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>188992</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1600934</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>46068</xdr:rowOff>
     </xdr:to>
@@ -1616,6 +2222,94 @@
         <a:xfrm>
           <a:off x="6295796" y="4712274"/>
           <a:ext cx="2716354" cy="1239294"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>360217</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>70090</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1603176</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>46068</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15226E65-FB16-44AE-B188-699C7F9A01F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7523017" y="4718290"/>
+          <a:ext cx="2650417" cy="1309478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>360217</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>70090</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1605418</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>46068</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3795C349-F99A-44B5-B9C8-66F208A9CB6A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7523017" y="4718290"/>
+          <a:ext cx="2652659" cy="1309478"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1951,7 +2645,7 @@
       <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="60" t="s">
+      <c r="E5" s="51" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -1977,16 +2671,16 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="60" t="s">
+      <c r="B6" s="51" t="s">
         <v>240</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="60" t="s">
+      <c r="E6" s="51" t="s">
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -2043,7 +2737,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="60" t="s">
+      <c r="D8" s="51" t="s">
         <v>241</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -2066,7 +2760,7 @@
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="51" t="s">
         <v>229</v>
       </c>
       <c r="C9" s="2"/>
@@ -2089,11 +2783,11 @@
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="60" t="s">
+      <c r="B10" s="51" t="s">
         <v>239</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="60" t="s">
+      <c r="D10" s="51" t="s">
         <v>242</v>
       </c>
       <c r="E10" s="2"/>
@@ -2105,18 +2799,18 @@
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="60" t="s">
+      <c r="J10" s="51" t="s">
         <v>254</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="60" t="s">
+      <c r="B11" s="51" t="s">
         <v>238</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="60" t="s">
+      <c r="D11" s="51" t="s">
         <v>254</v>
       </c>
       <c r="E11" s="2"/>
@@ -2135,16 +2829,16 @@
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="60" t="s">
+      <c r="B12" s="51" t="s">
         <v>237</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="60" t="s">
+      <c r="F12" s="51" t="s">
         <v>250</v>
       </c>
-      <c r="G12" s="60" t="s">
+      <c r="G12" s="51" t="s">
         <v>253</v>
       </c>
       <c r="H12" s="2"/>
@@ -2161,7 +2855,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="60" t="s">
+      <c r="G13" s="51" t="s">
         <v>250</v>
       </c>
       <c r="H13" s="2"/>
@@ -2262,18 +2956,18 @@
       <c r="L20" s="2"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B22" s="53" t="s">
+      <c r="B22" s="54" t="s">
         <v>228</v>
       </c>
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="48"/>
-    </row>
-    <row r="24" spans="2:12" s="18" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="18" t="s">
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="44"/>
+    </row>
+    <row r="24" spans="2:12" s="14" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="14" t="s">
         <v>236</v>
       </c>
     </row>
@@ -2341,51 +3035,51 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="61" t="s">
+      <c r="C5" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="61" t="s">
+      <c r="D5" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="60" t="s">
+      <c r="E5" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="61" t="s">
+      <c r="F5" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="61" t="s">
+      <c r="G5" s="52" t="s">
         <v>248</v>
       </c>
-      <c r="H5" s="61" t="s">
+      <c r="H5" s="52" t="s">
         <v>251</v>
       </c>
-      <c r="I5" s="61" t="s">
+      <c r="I5" s="52" t="s">
         <v>255</v>
       </c>
-      <c r="J5" s="61" t="s">
+      <c r="J5" s="52" t="s">
         <v>257</v>
       </c>
-      <c r="K5" s="61" t="s">
+      <c r="K5" s="52" t="s">
         <v>263</v>
       </c>
-      <c r="L5" s="61" t="s">
+      <c r="L5" s="52" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="60" t="s">
+      <c r="B6" s="51" t="s">
         <v>240</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="61" t="s">
+      <c r="E6" s="52" t="s">
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -2394,13 +3088,13 @@
       <c r="G6" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="H6" s="61" t="s">
+      <c r="H6" s="52" t="s">
         <v>252</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="J6" s="61" t="s">
+      <c r="J6" s="52" t="s">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="s">
@@ -2442,7 +3136,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="60" t="s">
+      <c r="D8" s="51" t="s">
         <v>241</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -2465,7 +3159,7 @@
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="51" t="s">
         <v>229</v>
       </c>
       <c r="C9" s="2"/>
@@ -2488,11 +3182,11 @@
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="60" t="s">
+      <c r="B10" s="51" t="s">
         <v>239</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="60" t="s">
+      <c r="D10" s="51" t="s">
         <v>242</v>
       </c>
       <c r="E10" s="2"/>
@@ -2504,18 +3198,18 @@
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="60" t="s">
+      <c r="J10" s="51" t="s">
         <v>254</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="60" t="s">
+      <c r="B11" s="51" t="s">
         <v>238</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="60" t="s">
+      <c r="D11" s="51" t="s">
         <v>254</v>
       </c>
       <c r="E11" s="2"/>
@@ -2534,16 +3228,16 @@
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="60" t="s">
+      <c r="B12" s="51" t="s">
         <v>237</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="60" t="s">
+      <c r="F12" s="51" t="s">
         <v>250</v>
       </c>
-      <c r="G12" s="60" t="s">
+      <c r="G12" s="51" t="s">
         <v>253</v>
       </c>
       <c r="H12" s="2"/>
@@ -2560,7 +3254,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="60" t="s">
+      <c r="G13" s="51" t="s">
         <v>250</v>
       </c>
       <c r="H13" s="2"/>
@@ -2661,16 +3355,16 @@
       <c r="L20" s="2"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B22" s="53"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="48"/>
-    </row>
-    <row r="24" spans="2:12" s="18" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="18" t="s">
+      <c r="B22" s="54"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="44"/>
+    </row>
+    <row r="24" spans="2:12" s="14" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="14" t="s">
         <v>236</v>
       </c>
     </row>
@@ -2695,7 +3389,7 @@
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B31" s="62" t="s">
+      <c r="B31" s="53" t="s">
         <v>268</v>
       </c>
     </row>
@@ -2731,8 +3425,8 @@
       <c r="L2" t="s">
         <v>224</v>
       </c>
-      <c r="M2" s="50"/>
-      <c r="N2" s="23"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="19"/>
       <c r="O2" t="s">
         <v>153</v>
       </c>
@@ -2752,10 +3446,10 @@
       <c r="B4" t="s">
         <v>82</v>
       </c>
-      <c r="P4" s="51"/>
+      <c r="P4" s="47"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="N5" s="51"/>
+      <c r="N5" s="47"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
@@ -2771,7 +3465,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D8" s="5"/>
-      <c r="P8" s="24" t="s">
+      <c r="P8" s="20" t="s">
         <v>59</v>
       </c>
       <c r="Q8" t="s">
@@ -2797,7 +3491,7 @@
       <c r="I9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="21" t="s">
         <v>0</v>
       </c>
       <c r="L9" s="6" t="s">
@@ -2809,13 +3503,13 @@
       <c r="N9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="25" t="s">
+      <c r="O9" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="P9" s="24" t="s">
+      <c r="P9" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="Q9" s="22" t="s">
+      <c r="Q9" s="18" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2838,7 +3532,7 @@
       <c r="I10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="21" t="s">
         <v>22</v>
       </c>
       <c r="L10" s="4" t="s">
@@ -2850,13 +3544,13 @@
       <c r="N10" s="4">
         <v>20</v>
       </c>
-      <c r="O10" s="25" t="s">
+      <c r="O10" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="P10" s="26" t="s">
+      <c r="P10" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="Q10" s="27" t="s">
+      <c r="Q10" s="23" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2879,7 +3573,7 @@
       <c r="I11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="21" t="s">
         <v>24</v>
       </c>
       <c r="L11" s="4" t="s">
@@ -2891,7 +3585,7 @@
       <c r="N11" s="4">
         <v>30</v>
       </c>
-      <c r="O11" s="25" t="s">
+      <c r="O11" s="21" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2914,7 +3608,7 @@
       <c r="I12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="21" t="s">
         <v>24</v>
       </c>
       <c r="L12" s="4" t="s">
@@ -2926,7 +3620,7 @@
       <c r="N12" s="4">
         <v>60</v>
       </c>
-      <c r="O12" s="25" t="s">
+      <c r="O12" s="21" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2946,12 +3640,12 @@
       <c r="Q13" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="R13" s="55" t="s">
+      <c r="R13" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="S13" s="55"/>
-      <c r="T13" s="55"/>
-      <c r="U13" s="55"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="56"/>
+      <c r="U13" s="56"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D14" s="5"/>
@@ -2964,10 +3658,10 @@
       <c r="Q14" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="R14" s="55"/>
-      <c r="S14" s="55"/>
-      <c r="T14" s="55"/>
-      <c r="U14" s="55"/>
+      <c r="R14" s="56"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="56"/>
+      <c r="U14" s="56"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
@@ -2975,7 +3669,7 @@
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="J16" s="51"/>
+      <c r="J16" s="47"/>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
@@ -3216,7 +3910,7 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
-      <c r="G32" s="23" t="s">
+      <c r="G32" s="19" t="s">
         <v>205</v>
       </c>
     </row>
@@ -3226,36 +3920,36 @@
       </c>
     </row>
     <row r="36" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
+      <c r="I36" s="44"/>
+      <c r="J36" s="44"/>
     </row>
     <row r="37" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I37" s="48"/>
-      <c r="J37" s="48"/>
+      <c r="I37" s="44"/>
+      <c r="J37" s="44"/>
     </row>
     <row r="38" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I38" s="48"/>
-      <c r="J38" s="48"/>
+      <c r="I38" s="44"/>
+      <c r="J38" s="44"/>
     </row>
     <row r="39" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I39" s="48"/>
-      <c r="J39" s="48"/>
+      <c r="I39" s="44"/>
+      <c r="J39" s="44"/>
     </row>
     <row r="40" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I40" s="48"/>
-      <c r="J40" s="48"/>
+      <c r="I40" s="44"/>
+      <c r="J40" s="44"/>
     </row>
     <row r="41" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I41" s="48"/>
-      <c r="J41" s="48"/>
+      <c r="I41" s="44"/>
+      <c r="J41" s="44"/>
     </row>
     <row r="42" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I42" s="52"/>
-      <c r="J42" s="52"/>
+      <c r="I42" s="48"/>
+      <c r="J42" s="48"/>
     </row>
     <row r="43" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I43" s="48"/>
-      <c r="J43" s="48"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3294,13 +3988,13 @@
       <c r="E4" t="s">
         <v>79</v>
       </c>
-      <c r="P4" s="19" t="s">
+      <c r="P4" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="T4" s="19" t="s">
+      <c r="T4" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="U4" s="19"/>
+      <c r="U4" s="15"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="E5" t="s">
@@ -3430,20 +4124,20 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="P10" s="20" t="s">
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="P10" s="16" t="s">
         <v>83</v>
       </c>
       <c r="T10" s="4" t="s">
@@ -3534,18 +4228,18 @@
       <c r="Y16" s="9"/>
     </row>
     <row r="18" spans="3:35" x14ac:dyDescent="0.25">
-      <c r="T18" s="21" t="s">
+      <c r="T18" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="U18" s="20"/>
-      <c r="V18" s="20"/>
+      <c r="U18" s="16"/>
+      <c r="V18" s="16"/>
       <c r="W18" s="5"/>
     </row>
     <row r="19" spans="3:35" x14ac:dyDescent="0.25">
-      <c r="P19" s="59" t="s">
+      <c r="P19" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="Q19" s="59"/>
+      <c r="Q19" s="60"/>
       <c r="T19" s="4" t="s">
         <v>9</v>
       </c>
@@ -3563,10 +4257,10 @@
       <c r="P20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="Q20" s="58" t="s">
+      <c r="Q20" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="R20" s="58"/>
+      <c r="R20" s="59"/>
       <c r="T20" s="4" t="s">
         <v>94</v>
       </c>
@@ -3584,10 +4278,10 @@
       <c r="P21" s="4">
         <v>1</v>
       </c>
-      <c r="Q21" s="58" t="s">
+      <c r="Q21" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="R21" s="58"/>
+      <c r="R21" s="59"/>
       <c r="T21" s="4" t="s">
         <v>94</v>
       </c>
@@ -3605,10 +4299,10 @@
       <c r="P22" s="4">
         <v>2</v>
       </c>
-      <c r="Q22" s="58" t="s">
+      <c r="Q22" s="59" t="s">
         <v>100</v>
       </c>
-      <c r="R22" s="58"/>
+      <c r="R22" s="59"/>
       <c r="T22" s="4" t="s">
         <v>94</v>
       </c>
@@ -3626,10 +4320,10 @@
       <c r="P23" s="4">
         <v>3</v>
       </c>
-      <c r="Q23" s="58" t="s">
+      <c r="Q23" s="59" t="s">
         <v>101</v>
       </c>
-      <c r="R23" s="58"/>
+      <c r="R23" s="59"/>
       <c r="T23" s="4"/>
       <c r="U23" s="4"/>
       <c r="V23" s="4"/>
@@ -3648,10 +4342,10 @@
       <c r="P24" s="4">
         <v>4</v>
       </c>
-      <c r="Q24" s="58" t="s">
+      <c r="Q24" s="59" t="s">
         <v>102</v>
       </c>
-      <c r="R24" s="58"/>
+      <c r="R24" s="59"/>
       <c r="T24" s="4" t="s">
         <v>95</v>
       </c>
@@ -3672,47 +4366,47 @@
       </c>
     </row>
     <row r="28" spans="3:35" x14ac:dyDescent="0.25">
-      <c r="T28" s="21" t="s">
+      <c r="T28" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="U28" s="21"/>
-      <c r="X28" s="21" t="s">
+      <c r="U28" s="17"/>
+      <c r="X28" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="Y28" s="21"/>
-      <c r="AA28" s="19" t="s">
+      <c r="Y28" s="17"/>
+      <c r="AA28" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="AD28" s="46" t="s">
+      <c r="AD28" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="AF28" s="19" t="s">
+      <c r="AF28" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="29" spans="3:35" x14ac:dyDescent="0.25">
-      <c r="C29" s="20" t="s">
+      <c r="C29" s="16" t="s">
         <v>121</v>
       </c>
       <c r="F29" t="s">
         <v>212</v>
       </c>
-      <c r="H29" s="20" t="s">
+      <c r="H29" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="J29" s="30" t="s">
+      <c r="J29" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="P29" s="20" t="s">
+      <c r="P29" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="T29" s="39" t="s">
+      <c r="T29" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="U29" s="39" t="s">
+      <c r="U29" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="V29" s="28" t="s">
+      <c r="V29" s="24" t="s">
         <v>158</v>
       </c>
       <c r="X29" s="6" t="s">
@@ -3721,7 +4415,7 @@
       <c r="Y29" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AA29" s="42" t="s">
+      <c r="AA29" s="38" t="s">
         <v>20</v>
       </c>
       <c r="AB29" s="4" t="s">
@@ -3730,10 +4424,10 @@
       <c r="AC29" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="AD29" s="44" t="s">
+      <c r="AD29" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="AF29" s="42" t="s">
+      <c r="AF29" s="38" t="s">
         <v>9</v>
       </c>
       <c r="AG29" s="4" t="s">
@@ -3742,7 +4436,7 @@
       <c r="AH29" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="AI29" s="42" t="s">
+      <c r="AI29" s="38" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3750,29 +4444,29 @@
       <c r="C30" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D30" s="47" t="s">
+      <c r="D30" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="E30" s="47" t="s">
+      <c r="E30" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="F30" s="25" t="s">
+      <c r="F30" s="21" t="s">
         <v>128</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="I30" s="47" t="s">
+      <c r="I30" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J30" s="31" t="s">
+      <c r="J30" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="K30" s="34" t="s">
+      <c r="K30" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="L30" s="34"/>
-      <c r="M30" s="34"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
       <c r="P30" s="6" t="s">
         <v>122</v>
       </c>
@@ -3782,13 +4476,13 @@
       <c r="R30" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="T30" s="28" t="s">
+      <c r="T30" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="U30" s="28" t="s">
+      <c r="U30" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="V30" s="28">
+      <c r="V30" s="24">
         <v>5</v>
       </c>
       <c r="X30" s="4" t="s">
@@ -3797,58 +4491,58 @@
       <c r="Y30" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="AA30" s="43" t="s">
+      <c r="AA30" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="AB30" s="41" t="s">
+      <c r="AB30" s="37" t="s">
         <v>192</v>
       </c>
       <c r="AC30" s="4">
         <v>225</v>
       </c>
-      <c r="AD30" s="43" t="s">
+      <c r="AD30" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="AF30" s="43" t="s">
+      <c r="AF30" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="AG30" s="41" t="s">
+      <c r="AG30" s="37" t="s">
         <v>196</v>
       </c>
       <c r="AH30" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="AI30" s="43" t="s">
+      <c r="AI30" s="39" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="31" spans="3:35" x14ac:dyDescent="0.25">
-      <c r="C31" s="47" t="s">
+      <c r="C31" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="D31" s="47" t="s">
+      <c r="D31" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="47">
+      <c r="E31" s="43">
         <v>8</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="H31" s="47" t="s">
+      <c r="H31" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="I31" s="47" t="s">
+      <c r="I31" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="J31" s="32" t="s">
+      <c r="J31" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="K31" s="35" t="s">
+      <c r="K31" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="L31" s="36"/>
-      <c r="M31" s="34"/>
+      <c r="L31" s="32"/>
+      <c r="M31" s="30"/>
       <c r="P31" s="4" t="s">
         <v>125</v>
       </c>
@@ -3858,13 +4552,13 @@
       <c r="R31" s="3">
         <v>7.8</v>
       </c>
-      <c r="T31" s="28" t="s">
+      <c r="T31" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="U31" s="28" t="s">
+      <c r="U31" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="V31" s="28">
+      <c r="V31" s="24">
         <v>6</v>
       </c>
       <c r="X31" s="4" t="s">
@@ -3873,51 +4567,51 @@
       <c r="Y31" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AA31" s="43" t="s">
+      <c r="AA31" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="AB31" s="41" t="s">
+      <c r="AB31" s="37" t="s">
         <v>193</v>
       </c>
       <c r="AC31" s="4">
         <v>0</v>
       </c>
-      <c r="AD31" s="43" t="s">
+      <c r="AD31" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="AF31" s="43" t="s">
+      <c r="AF31" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="AG31" s="41" t="s">
+      <c r="AG31" s="37" t="s">
         <v>197</v>
       </c>
       <c r="AH31" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="AI31" s="43" t="s">
+      <c r="AI31" s="39" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="32" spans="3:35" x14ac:dyDescent="0.25">
-      <c r="C32" s="47" t="s">
+      <c r="C32" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="47" t="s">
+      <c r="D32" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="E32" s="47">
+      <c r="E32" s="43">
         <v>6</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="H32" s="47" t="s">
+      <c r="H32" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="I32" s="47" t="s">
+      <c r="I32" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="J32" s="32" t="s">
+      <c r="J32" s="28" t="s">
         <v>126</v>
       </c>
       <c r="P32" s="4" t="s">
@@ -3929,13 +4623,13 @@
       <c r="R32" s="3">
         <v>8</v>
       </c>
-      <c r="T32" s="28" t="s">
+      <c r="T32" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="U32" s="28" t="s">
+      <c r="U32" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="V32" s="28">
+      <c r="V32" s="24">
         <v>7</v>
       </c>
       <c r="X32" s="4" t="s">
@@ -3944,51 +4638,51 @@
       <c r="Y32" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="AA32" s="43" t="s">
+      <c r="AA32" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="AB32" s="41" t="s">
+      <c r="AB32" s="37" t="s">
         <v>194</v>
       </c>
       <c r="AC32" s="4">
         <v>125</v>
       </c>
-      <c r="AD32" s="43" t="s">
+      <c r="AD32" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="AF32" s="43" t="s">
+      <c r="AF32" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="AG32" s="41" t="s">
+      <c r="AG32" s="37" t="s">
         <v>198</v>
       </c>
       <c r="AH32" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="AI32" s="43" t="s">
+      <c r="AI32" s="39" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="33" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C33" s="47" t="s">
+      <c r="C33" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="D33" s="47" t="s">
+      <c r="D33" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="E33" s="47">
+      <c r="E33" s="43">
         <v>9</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="H33" s="47" t="s">
+      <c r="H33" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="I33" s="47" t="s">
+      <c r="I33" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="J33" s="32" t="s">
+      <c r="J33" s="28" t="s">
         <v>125</v>
       </c>
       <c r="P33" s="4" t="s">
@@ -4000,48 +4694,48 @@
       <c r="R33" s="3">
         <v>9.5</v>
       </c>
-      <c r="T33" s="28" t="s">
+      <c r="T33" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="U33" s="28" t="s">
+      <c r="U33" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="V33" s="28">
+      <c r="V33" s="24">
         <v>5</v>
       </c>
-      <c r="AA33" s="43" t="s">
+      <c r="AA33" s="39" t="s">
         <v>191</v>
       </c>
-      <c r="AB33" s="41" t="s">
+      <c r="AB33" s="37" t="s">
         <v>195</v>
       </c>
       <c r="AC33" s="4">
         <v>220</v>
       </c>
-      <c r="AD33" s="43" t="s">
+      <c r="AD33" s="39" t="s">
         <v>202</v>
       </c>
-      <c r="AF33" s="43" t="s">
+      <c r="AF33" s="39" t="s">
         <v>202</v>
       </c>
-      <c r="AG33" s="41" t="s">
+      <c r="AG33" s="37" t="s">
         <v>198</v>
       </c>
       <c r="AH33" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="AI33" s="43" t="s">
+      <c r="AI33" s="39" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="34" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C34" s="47" t="s">
+      <c r="C34" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="D34" s="47" t="s">
+      <c r="D34" s="43" t="s">
         <v>144</v>
       </c>
-      <c r="E34" s="47">
+      <c r="E34" s="43">
         <v>7</v>
       </c>
       <c r="F34" s="8" t="s">
@@ -4056,24 +4750,24 @@
       <c r="R34" s="3">
         <v>2</v>
       </c>
-      <c r="T34" s="37" t="s">
+      <c r="T34" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="U34" s="37" t="s">
+      <c r="U34" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="V34" s="28">
+      <c r="V34" s="24">
         <v>9</v>
       </c>
     </row>
     <row r="35" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C35" s="47" t="s">
+      <c r="C35" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="D35" s="47" t="s">
+      <c r="D35" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="E35" s="47">
+      <c r="E35" s="43">
         <v>7</v>
       </c>
       <c r="F35" s="4" t="s">
@@ -4090,7 +4784,7 @@
       </c>
     </row>
     <row r="37" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C37" s="33" t="s">
+      <c r="C37" s="29" t="s">
         <v>151</v>
       </c>
       <c r="D37" s="9"/>
@@ -4102,7 +4796,7 @@
       <c r="J37" s="9"/>
       <c r="K37" s="9"/>
       <c r="L37" s="9"/>
-      <c r="P37" s="33" t="s">
+      <c r="P37" s="29" t="s">
         <v>211</v>
       </c>
       <c r="Q37" s="9"/>
@@ -4161,7 +4855,7 @@
       <c r="C41" t="s">
         <v>136</v>
       </c>
-      <c r="AA41" s="49" t="s">
+      <c r="AA41" s="45" t="s">
         <v>145</v>
       </c>
     </row>
@@ -4169,16 +4863,16 @@
       <c r="C42" t="s">
         <v>139</v>
       </c>
-      <c r="AA42" s="45" t="s">
+      <c r="AA42" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="AB42" s="45"/>
-      <c r="AC42" s="45"/>
-      <c r="AD42" s="45"/>
-      <c r="AE42" s="45"/>
-      <c r="AF42" s="45"/>
-      <c r="AG42" s="45"/>
-      <c r="AH42" s="45"/>
+      <c r="AB42" s="41"/>
+      <c r="AC42" s="41"/>
+      <c r="AD42" s="41"/>
+      <c r="AE42" s="41"/>
+      <c r="AF42" s="41"/>
+      <c r="AG42" s="41"/>
+      <c r="AH42" s="41"/>
     </row>
     <row r="43" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
@@ -4189,7 +4883,7 @@
       <c r="C44" t="s">
         <v>145</v>
       </c>
-      <c r="O44" s="29" t="s">
+      <c r="O44" s="25" t="s">
         <v>159</v>
       </c>
       <c r="T44" t="s">
@@ -4203,16 +4897,16 @@
       <c r="C45" t="s">
         <v>141</v>
       </c>
-      <c r="O45" s="38" t="s">
+      <c r="O45" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="P45" s="28" t="s">
+      <c r="P45" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="Q45" s="28" t="s">
+      <c r="Q45" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="R45" s="28" t="s">
+      <c r="R45" s="24" t="s">
         <v>161</v>
       </c>
       <c r="T45" t="s">
@@ -4235,25 +4929,25 @@
       <c r="N46" t="s">
         <v>175</v>
       </c>
-      <c r="O46" s="28">
+      <c r="O46" s="24">
         <v>1</v>
       </c>
-      <c r="P46" s="28">
+      <c r="P46" s="24">
         <v>1</v>
       </c>
-      <c r="Q46" s="40" t="s">
+      <c r="Q46" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="R46" s="40" t="s">
+      <c r="R46" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="T46" s="28" t="s">
+      <c r="T46" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="U46" s="28">
+      <c r="U46" s="24">
         <v>1</v>
       </c>
-      <c r="V46" s="28">
+      <c r="V46" s="24">
         <v>8</v>
       </c>
       <c r="Y46" t="s">
@@ -4267,25 +4961,25 @@
       <c r="C47" t="s">
         <v>218</v>
       </c>
-      <c r="O47" s="28">
+      <c r="O47" s="24">
         <v>2</v>
       </c>
-      <c r="P47" s="28">
+      <c r="P47" s="24">
         <v>2</v>
       </c>
-      <c r="Q47" s="40" t="s">
+      <c r="Q47" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="R47" s="40" t="s">
+      <c r="R47" s="36" t="s">
         <v>177</v>
       </c>
-      <c r="T47" s="28" t="s">
+      <c r="T47" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="U47" s="28">
+      <c r="U47" s="24">
         <v>2</v>
       </c>
-      <c r="V47" s="28">
+      <c r="V47" s="24">
         <v>8</v>
       </c>
       <c r="Y47" t="s">
@@ -4296,146 +4990,146 @@
       </c>
     </row>
     <row r="48" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C48" s="56" t="s">
+      <c r="C48" s="57" t="s">
         <v>220</v>
       </c>
-      <c r="D48" s="54"/>
-      <c r="E48" s="54"/>
-      <c r="F48" s="54"/>
-      <c r="G48" s="54"/>
-      <c r="H48" s="54"/>
-      <c r="I48" s="54"/>
-      <c r="J48" s="54"/>
-      <c r="O48" s="28">
+      <c r="D48" s="55"/>
+      <c r="E48" s="55"/>
+      <c r="F48" s="55"/>
+      <c r="G48" s="55"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="55"/>
+      <c r="J48" s="55"/>
+      <c r="O48" s="24">
         <v>3</v>
       </c>
-      <c r="P48" s="28">
+      <c r="P48" s="24">
         <v>3</v>
       </c>
-      <c r="Q48" s="40" t="s">
+      <c r="Q48" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="R48" s="40" t="s">
+      <c r="R48" s="36" t="s">
         <v>172</v>
       </c>
-      <c r="T48" s="28" t="s">
+      <c r="T48" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="U48" s="28">
+      <c r="U48" s="24">
         <v>1</v>
       </c>
-      <c r="V48" s="28">
+      <c r="V48" s="24">
         <v>9</v>
       </c>
-      <c r="AE48" s="42" t="s">
+      <c r="AE48" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="AF48" s="43" t="s">
+      <c r="AF48" s="39" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="49" spans="3:32" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C49" s="57" t="s">
+      <c r="C49" s="58" t="s">
         <v>219</v>
       </c>
-      <c r="D49" s="57"/>
-      <c r="E49" s="57"/>
-      <c r="F49" s="57"/>
-      <c r="G49" s="57"/>
-      <c r="H49" s="57"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="57"/>
-      <c r="O49" s="28">
+      <c r="D49" s="58"/>
+      <c r="E49" s="58"/>
+      <c r="F49" s="58"/>
+      <c r="G49" s="58"/>
+      <c r="H49" s="58"/>
+      <c r="I49" s="58"/>
+      <c r="J49" s="58"/>
+      <c r="O49" s="24">
         <v>4</v>
       </c>
-      <c r="P49" s="28">
+      <c r="P49" s="24">
         <v>4</v>
       </c>
-      <c r="Q49" s="40" t="s">
+      <c r="Q49" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="R49" s="40" t="s">
+      <c r="R49" s="36" t="s">
         <v>178</v>
       </c>
-      <c r="T49" s="28" t="s">
+      <c r="T49" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="U49" s="28">
+      <c r="U49" s="24">
         <v>1</v>
       </c>
-      <c r="V49" s="28">
+      <c r="V49" s="24">
         <v>9</v>
       </c>
-      <c r="AE49" s="43" t="s">
+      <c r="AE49" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="AF49" s="43" t="s">
+      <c r="AF49" s="39" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="50" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="O50" s="28">
+      <c r="O50" s="24">
         <v>5</v>
       </c>
-      <c r="P50" s="28">
+      <c r="P50" s="24">
         <v>5</v>
       </c>
-      <c r="Q50" s="40" t="s">
+      <c r="Q50" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="R50" s="40" t="s">
+      <c r="R50" s="36" t="s">
         <v>173</v>
       </c>
-      <c r="AE50" s="43" t="s">
+      <c r="AE50" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="AF50" s="43" t="s">
+      <c r="AF50" s="39" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="51" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="O51" s="28">
+      <c r="O51" s="24">
         <v>6</v>
       </c>
-      <c r="P51" s="28">
+      <c r="P51" s="24">
         <v>6</v>
       </c>
-      <c r="Q51" s="40" t="s">
+      <c r="Q51" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="R51" s="40" t="s">
+      <c r="R51" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="AE51" s="43" t="s">
+      <c r="AE51" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="AF51" s="43" t="s">
+      <c r="AF51" s="39" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="52" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C52" s="20" t="s">
+      <c r="C52" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="H52" s="20" t="s">
+      <c r="H52" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="O52" s="28">
+      <c r="O52" s="24">
         <v>7</v>
       </c>
-      <c r="P52" s="28">
+      <c r="P52" s="24">
         <v>7</v>
       </c>
-      <c r="Q52" s="40" t="s">
+      <c r="Q52" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="R52" s="40" t="s">
+      <c r="R52" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="AE52" s="43" t="s">
+      <c r="AE52" s="39" t="s">
         <v>191</v>
       </c>
-      <c r="AF52" s="43" t="s">
+      <c r="AF52" s="39" t="s">
         <v>202</v>
       </c>
     </row>
@@ -4443,10 +5137,10 @@
       <c r="C53" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D53" s="47" t="s">
+      <c r="D53" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="E53" s="47" t="s">
+      <c r="E53" s="43" t="s">
         <v>124</v>
       </c>
       <c r="F53" t="s">
@@ -4455,70 +5149,70 @@
       <c r="H53" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="I53" s="47" t="s">
+      <c r="I53" s="43" t="s">
         <v>39</v>
       </c>
       <c r="J53" t="s">
         <v>121</v>
       </c>
-      <c r="O53" s="28">
+      <c r="O53" s="24">
         <v>8</v>
       </c>
-      <c r="P53" s="28">
+      <c r="P53" s="24">
         <v>8</v>
       </c>
-      <c r="Q53" s="40" t="s">
+      <c r="Q53" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="R53" s="40" t="s">
+      <c r="R53" s="36" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="54" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C54" s="47" t="s">
+      <c r="C54" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="D54" s="47" t="s">
+      <c r="D54" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="E54" s="47">
+      <c r="E54" s="43">
         <v>8</v>
       </c>
       <c r="F54" t="s">
         <v>130</v>
       </c>
-      <c r="H54" s="47"/>
-      <c r="I54" s="47"/>
-      <c r="O54" s="28">
+      <c r="H54" s="43"/>
+      <c r="I54" s="43"/>
+      <c r="O54" s="24">
         <v>9</v>
       </c>
-      <c r="P54" s="28">
+      <c r="P54" s="24">
         <v>1</v>
       </c>
-      <c r="Q54" s="40" t="s">
+      <c r="Q54" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="R54" s="40" t="s">
+      <c r="R54" s="36" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="55" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C55" s="47" t="s">
+      <c r="C55" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="D55" s="47" t="s">
+      <c r="D55" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="E55" s="47">
+      <c r="E55" s="43">
         <v>6</v>
       </c>
       <c r="F55" t="s">
         <v>130</v>
       </c>
-      <c r="H55" s="47" t="s">
+      <c r="H55" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="I55" s="47" t="s">
+      <c r="I55" s="43" t="s">
         <v>134</v>
       </c>
       <c r="J55" t="s">
@@ -4527,156 +5221,156 @@
       <c r="N55" t="s">
         <v>176</v>
       </c>
-      <c r="O55" s="28">
+      <c r="O55" s="24">
         <v>10</v>
       </c>
-      <c r="P55" s="28">
+      <c r="P55" s="24">
         <v>2</v>
       </c>
-      <c r="Q55" s="40" t="s">
+      <c r="Q55" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="R55" s="40" t="s">
+      <c r="R55" s="36" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="56" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C56" s="47" t="s">
+      <c r="C56" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="D56" s="47" t="s">
+      <c r="D56" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="E56" s="47">
+      <c r="E56" s="43">
         <v>9</v>
       </c>
       <c r="F56" t="s">
         <v>132</v>
       </c>
-      <c r="H56" s="47" t="s">
+      <c r="H56" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="I56" s="47" t="s">
+      <c r="I56" s="43" t="s">
         <v>135</v>
       </c>
       <c r="J56" t="s">
         <v>125</v>
       </c>
-      <c r="O56" s="28">
+      <c r="O56" s="24">
         <v>11</v>
       </c>
-      <c r="P56" s="28">
+      <c r="P56" s="24">
         <v>3</v>
       </c>
-      <c r="Q56" s="40" t="s">
+      <c r="Q56" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="R56" s="40" t="s">
+      <c r="R56" s="36" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="57" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C57" s="47" t="s">
+      <c r="C57" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="D57" s="47" t="s">
+      <c r="D57" s="43" t="s">
         <v>144</v>
       </c>
-      <c r="E57" s="47">
+      <c r="E57" s="43">
         <v>7</v>
       </c>
       <c r="F57" t="s">
         <v>131</v>
       </c>
-      <c r="O57" s="28">
+      <c r="O57" s="24">
         <v>12</v>
       </c>
-      <c r="P57" s="28">
+      <c r="P57" s="24">
         <v>4</v>
       </c>
-      <c r="Q57" s="40" t="s">
+      <c r="Q57" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="R57" s="40" t="s">
+      <c r="R57" s="36" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="58" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C58" s="47" t="s">
+      <c r="C58" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="D58" s="47" t="s">
+      <c r="D58" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="E58" s="47">
+      <c r="E58" s="43">
         <v>7</v>
       </c>
       <c r="F58" t="s">
         <v>132</v>
       </c>
-      <c r="O58" s="28">
+      <c r="O58" s="24">
         <v>13</v>
       </c>
-      <c r="P58" s="28">
+      <c r="P58" s="24">
         <v>5</v>
       </c>
-      <c r="Q58" s="40" t="s">
+      <c r="Q58" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="R58" s="40" t="s">
+      <c r="R58" s="36" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="59" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="O59" s="28">
+      <c r="O59" s="24">
         <v>14</v>
       </c>
-      <c r="P59" s="28">
+      <c r="P59" s="24">
         <v>6</v>
       </c>
-      <c r="Q59" s="40" t="s">
+      <c r="Q59" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="R59" s="40" t="s">
+      <c r="R59" s="36" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="60" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="O60" s="28">
+      <c r="O60" s="24">
         <v>15</v>
       </c>
-      <c r="P60" s="28">
+      <c r="P60" s="24">
         <v>7</v>
       </c>
-      <c r="Q60" s="40" t="s">
+      <c r="Q60" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="R60" s="40" t="s">
+      <c r="R60" s="36" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="61" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="O61" s="28">
+      <c r="O61" s="24">
         <v>16</v>
       </c>
-      <c r="P61" s="28">
+      <c r="P61" s="24">
         <v>8</v>
       </c>
-      <c r="Q61" s="40" t="s">
+      <c r="Q61" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="R61" s="40" t="s">
+      <c r="R61" s="36" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="71" spans="17:24" x14ac:dyDescent="0.25">
-      <c r="Q71" s="20" t="s">
+      <c r="Q71" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="W71" s="21" t="s">
+      <c r="W71" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="X71" s="21"/>
+      <c r="X71" s="17"/>
     </row>
     <row r="72" spans="17:24" x14ac:dyDescent="0.25">
       <c r="Q72" s="6" t="s">
@@ -4800,306 +5494,1191 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B2:N26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="B2:W63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" customWidth="1"/>
-    <col min="6" max="7" width="21.140625" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="5" max="5" width="22.5703125" customWidth="1"/>
+    <col min="6" max="6" width="21.140625" customWidth="1"/>
+    <col min="7" max="7" width="24.140625" customWidth="1"/>
     <col min="8" max="8" width="25" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="13" width="12.7109375" customWidth="1"/>
-    <col min="14" max="14" width="18.28515625" customWidth="1"/>
-    <col min="15" max="22" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="23.28515625" customWidth="1"/>
+    <col min="10" max="10" width="23" customWidth="1"/>
+    <col min="11" max="11" width="16.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.28515625" customWidth="1"/>
+    <col min="13" max="13" width="28.28515625" customWidth="1"/>
+    <col min="14" max="15" width="30" customWidth="1"/>
+    <col min="16" max="16" width="23.28515625" customWidth="1"/>
+    <col min="17" max="17" width="20.7109375" customWidth="1"/>
+    <col min="18" max="18" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>78</v>
+        <v>269</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="4" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="14"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-    </row>
-    <row r="5" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="17"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-    </row>
-    <row r="6" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="17"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-    </row>
-    <row r="7" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="3"/>
-    </row>
-    <row r="8" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="4"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="D3" s="49" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="61" t="s">
+        <v>271</v>
+      </c>
+      <c r="C4" s="62" t="s">
+        <v>272</v>
+      </c>
+      <c r="D4" s="62" t="s">
+        <v>273</v>
+      </c>
+      <c r="E4" s="62" t="s">
+        <v>274</v>
+      </c>
+      <c r="F4" s="62" t="s">
+        <v>275</v>
+      </c>
+      <c r="G4" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="H4" s="62" t="s">
+        <v>277</v>
+      </c>
+      <c r="I4" s="62" t="s">
+        <v>278</v>
+      </c>
+      <c r="J4" s="62" t="s">
+        <v>279</v>
+      </c>
+      <c r="K4" s="62" t="s">
+        <v>280</v>
+      </c>
+      <c r="L4" s="62" t="s">
+        <v>281</v>
+      </c>
+      <c r="M4" s="62" t="s">
+        <v>282</v>
+      </c>
+      <c r="N4" s="62" t="s">
+        <v>283</v>
+      </c>
+      <c r="O4" s="62" t="s">
+        <v>284</v>
+      </c>
+      <c r="P4" s="62" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q4" s="62" t="s">
+        <v>286</v>
+      </c>
+      <c r="R4" s="62" t="s">
+        <v>287</v>
+      </c>
+      <c r="S4" s="62" t="s">
+        <v>288</v>
+      </c>
+      <c r="T4" s="62" t="s">
+        <v>289</v>
+      </c>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+    </row>
+    <row r="5" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="63" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="63" t="s">
+        <v>291</v>
+      </c>
+      <c r="D5" s="63" t="s">
+        <v>292</v>
+      </c>
+      <c r="E5" s="63" t="s">
+        <v>293</v>
+      </c>
+      <c r="F5" s="63" t="s">
+        <v>294</v>
+      </c>
+      <c r="G5" s="63" t="s">
+        <v>295</v>
+      </c>
+      <c r="H5" s="63" t="s">
+        <v>296</v>
+      </c>
+      <c r="I5" s="63" t="s">
+        <v>297</v>
+      </c>
+      <c r="J5" s="63" t="s">
+        <v>298</v>
+      </c>
+      <c r="K5" s="63" t="s">
+        <v>299</v>
+      </c>
+      <c r="L5" s="63" t="s">
+        <v>300</v>
+      </c>
+      <c r="M5" s="63" t="s">
+        <v>301</v>
+      </c>
+      <c r="N5" s="63" t="s">
+        <v>302</v>
+      </c>
+      <c r="O5" s="63" t="s">
+        <v>303</v>
+      </c>
+      <c r="P5" s="63" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q5" s="63" t="s">
+        <v>305</v>
+      </c>
+      <c r="R5" s="63" t="s">
+        <v>306</v>
+      </c>
+      <c r="S5" s="63" t="s">
+        <v>307</v>
+      </c>
+      <c r="T5" s="63" t="s">
+        <v>308</v>
+      </c>
+      <c r="U5" s="63"/>
+      <c r="V5" s="63"/>
+      <c r="W5" s="63"/>
+    </row>
+    <row r="6" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="50" t="s">
+        <v>309</v>
+      </c>
+      <c r="C6" s="64" t="s">
+        <v>310</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>311</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="F6" s="63" t="s">
+        <v>313</v>
+      </c>
+      <c r="G6" s="50" t="s">
+        <v>314</v>
+      </c>
+      <c r="H6" s="50" t="s">
+        <v>315</v>
+      </c>
+      <c r="I6" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="J6" s="39" t="s">
+        <v>317</v>
+      </c>
+      <c r="K6" s="39" t="s">
+        <v>318</v>
+      </c>
+      <c r="L6" s="39" t="s">
+        <v>319</v>
+      </c>
+      <c r="M6" s="63" t="s">
+        <v>320</v>
+      </c>
+      <c r="N6" s="39" t="s">
+        <v>321</v>
+      </c>
+      <c r="O6" s="39" t="s">
+        <v>322</v>
+      </c>
+      <c r="P6" s="39" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q6" s="39" t="s">
+        <v>324</v>
+      </c>
+      <c r="R6" s="39" t="s">
+        <v>325</v>
+      </c>
+      <c r="S6" s="63" t="s">
+        <v>326</v>
+      </c>
+      <c r="T6" s="39" t="s">
+        <v>327</v>
+      </c>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="W6" s="39"/>
+    </row>
+    <row r="7" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="66" t="s">
+        <v>328</v>
+      </c>
+      <c r="C7" s="64" t="s">
+        <v>329</v>
+      </c>
+      <c r="D7" s="65" t="s">
+        <v>330</v>
+      </c>
+      <c r="E7" s="39"/>
+      <c r="F7" s="64" t="s">
+        <v>331</v>
+      </c>
+      <c r="G7" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="H7" s="50" t="s">
+        <v>333</v>
+      </c>
+      <c r="I7" s="39" t="s">
+        <v>334</v>
+      </c>
+      <c r="J7" s="39" t="s">
+        <v>335</v>
+      </c>
+      <c r="K7" s="67"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="39" t="s">
+        <v>336</v>
+      </c>
+      <c r="N7" s="50"/>
+      <c r="O7" s="50"/>
+      <c r="P7" s="50" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q7" s="50" t="s">
+        <v>338</v>
+      </c>
+      <c r="R7" s="50" t="s">
+        <v>339</v>
+      </c>
+      <c r="S7" s="50" t="s">
+        <v>340</v>
+      </c>
+      <c r="T7" s="39" t="s">
+        <v>341</v>
+      </c>
+      <c r="U7" s="50"/>
+      <c r="V7" s="50"/>
+      <c r="W7" s="50"/>
+    </row>
+    <row r="8" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="39"/>
+      <c r="C8" s="50" t="s">
+        <v>342</v>
+      </c>
+      <c r="D8" s="64" t="s">
+        <v>343</v>
+      </c>
+      <c r="E8" s="67"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="50" t="s">
+        <v>344</v>
+      </c>
+      <c r="H8" s="50" t="s">
+        <v>345</v>
+      </c>
+      <c r="I8" s="39" t="s">
+        <v>346</v>
+      </c>
+      <c r="J8" s="39" t="s">
+        <v>347</v>
+      </c>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39" t="s">
+        <v>348</v>
+      </c>
+      <c r="N8" s="50"/>
+      <c r="O8" s="50"/>
+      <c r="P8" s="66" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q8" s="50"/>
+      <c r="R8" s="50"/>
+      <c r="S8" s="50" t="s">
+        <v>350</v>
+      </c>
+      <c r="T8" s="50"/>
+      <c r="U8" s="50"/>
+      <c r="V8" s="50"/>
+      <c r="W8" s="50"/>
+    </row>
+    <row r="9" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="66"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="E9" s="39"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="66" t="s">
+        <v>352</v>
+      </c>
+      <c r="H9" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="I9" s="39" t="s">
+        <v>354</v>
+      </c>
+      <c r="J9" s="66" t="s">
+        <v>355</v>
+      </c>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="50"/>
+      <c r="O9" s="50"/>
+      <c r="P9" s="50"/>
+      <c r="Q9" s="50"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="66" t="s">
+        <v>308</v>
+      </c>
+      <c r="T9" s="50"/>
+      <c r="U9" s="50"/>
+      <c r="V9" s="50"/>
+      <c r="W9" s="50"/>
+    </row>
+    <row r="10" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="68"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="39" t="s">
+        <v>356</v>
+      </c>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39" t="s">
+        <v>357</v>
+      </c>
+      <c r="H10" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="I10" s="39" t="s">
+        <v>359</v>
+      </c>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="50"/>
+      <c r="O10" s="50"/>
+      <c r="P10" s="50"/>
+      <c r="Q10" s="50"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="50"/>
+      <c r="T10" s="50"/>
+      <c r="U10" s="50"/>
+      <c r="V10" s="50"/>
+      <c r="W10" s="50"/>
+    </row>
+    <row r="11" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="68"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="68" t="s">
+        <v>360</v>
+      </c>
+      <c r="H11" s="50" t="s">
+        <v>361</v>
+      </c>
+      <c r="I11" s="66" t="s">
+        <v>362</v>
+      </c>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="50"/>
+      <c r="O11" s="50"/>
+      <c r="P11" s="50"/>
+      <c r="Q11" s="50"/>
+      <c r="R11" s="50"/>
+      <c r="S11" s="50"/>
+      <c r="T11" s="50"/>
+      <c r="U11" s="50"/>
+      <c r="V11" s="50"/>
+      <c r="W11" s="50"/>
+    </row>
+    <row r="12" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="68"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="68" t="s">
+        <v>363</v>
+      </c>
+      <c r="H12" s="66" t="s">
+        <v>364</v>
+      </c>
+      <c r="I12" s="66" t="s">
+        <v>365</v>
+      </c>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="50"/>
+      <c r="W12" s="50"/>
+    </row>
+    <row r="13" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="39"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="50"/>
+      <c r="Q13" s="50"/>
+      <c r="R13" s="50"/>
+      <c r="S13" s="50"/>
+      <c r="T13" s="50"/>
+      <c r="U13" s="50"/>
+      <c r="V13" s="50"/>
+      <c r="W13" s="50"/>
+    </row>
+    <row r="14" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="50"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="50"/>
+      <c r="O14" s="50"/>
+      <c r="P14" s="50"/>
+      <c r="Q14" s="50"/>
+      <c r="R14" s="50"/>
+      <c r="S14" s="50"/>
+      <c r="T14" s="50"/>
+      <c r="U14" s="50"/>
+      <c r="V14" s="50"/>
+      <c r="W14" s="50"/>
+    </row>
+    <row r="15" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="50"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="39"/>
+      <c r="N15" s="50"/>
+      <c r="O15" s="50"/>
+      <c r="P15" s="50"/>
+      <c r="Q15" s="50"/>
+      <c r="R15" s="50"/>
+      <c r="S15" s="50"/>
+      <c r="T15" s="50"/>
+      <c r="U15" s="50"/>
+      <c r="V15" s="50"/>
+      <c r="W15" s="50"/>
+    </row>
+    <row r="16" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="50"/>
+      <c r="O16" s="50"/>
+      <c r="P16" s="50"/>
+      <c r="Q16" s="50"/>
+      <c r="R16" s="50"/>
+      <c r="S16" s="50"/>
+      <c r="T16" s="50"/>
+      <c r="U16" s="50"/>
+      <c r="V16" s="50"/>
+      <c r="W16" s="50"/>
+    </row>
+    <row r="17" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="50"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="39"/>
+      <c r="N17" s="50"/>
+      <c r="O17" s="50"/>
+      <c r="P17" s="50"/>
+      <c r="Q17" s="50"/>
+      <c r="R17" s="50"/>
+      <c r="S17" s="50"/>
+      <c r="T17" s="50"/>
+      <c r="U17" s="50"/>
+      <c r="V17" s="50"/>
+      <c r="W17" s="50"/>
+    </row>
+    <row r="18" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="50"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="50"/>
+      <c r="O18" s="50"/>
+      <c r="P18" s="50"/>
+      <c r="Q18" s="50"/>
+      <c r="R18" s="50"/>
+      <c r="S18" s="50"/>
+      <c r="T18" s="50"/>
+      <c r="U18" s="50"/>
+      <c r="V18" s="50"/>
+      <c r="W18" s="50"/>
+    </row>
+    <row r="19" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="50"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="50"/>
+      <c r="O19" s="50"/>
+      <c r="P19" s="50"/>
+      <c r="Q19" s="50"/>
+      <c r="R19" s="50"/>
+      <c r="S19" s="50"/>
+      <c r="T19" s="50"/>
+      <c r="U19" s="50"/>
+      <c r="V19" s="50"/>
+      <c r="W19" s="50"/>
+    </row>
+    <row r="20" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="50"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="50"/>
+      <c r="O20" s="50"/>
+      <c r="P20" s="50"/>
+      <c r="Q20" s="50"/>
+      <c r="R20" s="50"/>
+      <c r="S20" s="50"/>
+      <c r="T20" s="50"/>
+      <c r="U20" s="50"/>
+      <c r="V20" s="50"/>
+      <c r="W20" s="50"/>
+    </row>
+    <row r="22" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
+      <c r="L22" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="23" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="L23" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="24" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="L24" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="26" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
+      <c r="I26" t="s">
+        <v>271</v>
+      </c>
+      <c r="L26" t="s">
+        <v>272</v>
+      </c>
+      <c r="M26" s="69" t="s">
+        <v>369</v>
+      </c>
+      <c r="N26" s="69"/>
+      <c r="O26" s="5"/>
+    </row>
+    <row r="27" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
+      <c r="I27" t="s">
+        <v>290</v>
+      </c>
+      <c r="J27" t="s">
+        <v>309</v>
+      </c>
+      <c r="L27" t="s">
+        <v>291</v>
+      </c>
+      <c r="M27" t="s">
+        <v>291</v>
+      </c>
+      <c r="N27" t="s">
+        <v>329</v>
+      </c>
+      <c r="P27" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="28" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="I28" s="18">
+        <v>1</v>
+      </c>
+      <c r="J28" t="s">
+        <v>370</v>
+      </c>
+      <c r="L28" s="18">
+        <v>1</v>
+      </c>
+      <c r="M28" t="s">
+        <v>371</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="P28" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="29" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
         <v>109</v>
       </c>
+      <c r="I29" s="18">
+        <v>2</v>
+      </c>
+      <c r="J29" t="s">
+        <v>373</v>
+      </c>
+      <c r="L29" s="18">
+        <v>2</v>
+      </c>
+      <c r="M29" t="s">
+        <v>85</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="I30" s="18"/>
+      <c r="L30" s="18">
+        <v>3</v>
+      </c>
+      <c r="M30" t="s">
+        <v>86</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="I31" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="L31" s="18">
+        <v>4</v>
+      </c>
+      <c r="M31" t="s">
+        <v>374</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="I32" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="J32" s="39" t="s">
+        <v>313</v>
+      </c>
+      <c r="K32" s="39" t="s">
+        <v>331</v>
+      </c>
+      <c r="L32" s="18">
+        <v>5</v>
+      </c>
+      <c r="M32" t="s">
+        <v>375</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33" t="s">
+        <v>376</v>
+      </c>
+      <c r="K33" s="53" t="s">
+        <v>377</v>
+      </c>
+      <c r="L33" s="18">
+        <v>6</v>
+      </c>
+      <c r="M33" t="s">
+        <v>371</v>
+      </c>
+      <c r="N33">
+        <v>1</v>
+      </c>
+      <c r="P33" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>379</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34" t="s">
+        <v>376</v>
+      </c>
+      <c r="K34" s="53" t="s">
+        <v>380</v>
+      </c>
+      <c r="L34" s="18">
+        <v>7</v>
+      </c>
+      <c r="M34" t="s">
+        <v>85</v>
+      </c>
+      <c r="N34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>381</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="J35" t="s">
+        <v>382</v>
+      </c>
+      <c r="K35" s="53" t="s">
+        <v>383</v>
+      </c>
+      <c r="L35" s="18">
+        <v>8</v>
+      </c>
+      <c r="M35" t="s">
+        <v>86</v>
+      </c>
+      <c r="N35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>384</v>
+      </c>
+      <c r="I36" s="18"/>
+      <c r="L36" s="18">
+        <v>9</v>
+      </c>
+      <c r="M36" t="s">
+        <v>374</v>
+      </c>
+      <c r="N36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>385</v>
+      </c>
+      <c r="I37" s="18"/>
+      <c r="L37" s="18">
+        <v>10</v>
+      </c>
+      <c r="M37" t="s">
+        <v>375</v>
+      </c>
+      <c r="N37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>386</v>
+      </c>
+      <c r="M38" s="70" t="s">
+        <v>375</v>
+      </c>
+      <c r="N38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="I39" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="I40" t="s">
+        <v>311</v>
+      </c>
+      <c r="J40" t="s">
+        <v>388</v>
+      </c>
+      <c r="K40" t="s">
+        <v>389</v>
+      </c>
+      <c r="L40" t="s">
+        <v>351</v>
+      </c>
+      <c r="M40" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B41" s="71" t="s">
+        <v>282</v>
+      </c>
+      <c r="C41" s="71"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="71"/>
+      <c r="I41" s="18">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="K41" t="s">
+        <v>376</v>
+      </c>
+      <c r="L41" s="18">
+        <v>220</v>
+      </c>
+      <c r="M41">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B42" s="71" t="s">
+        <v>301</v>
+      </c>
+      <c r="C42" s="71" t="s">
+        <v>320</v>
+      </c>
+      <c r="D42" s="71" t="s">
+        <v>336</v>
+      </c>
+      <c r="E42" s="71" t="s">
+        <v>348</v>
+      </c>
+      <c r="I42" s="18">
+        <v>1</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42" t="s">
+        <v>382</v>
+      </c>
+      <c r="L42" s="18">
+        <v>230</v>
+      </c>
+      <c r="M42">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B43" s="49">
+        <v>1</v>
+      </c>
+      <c r="C43" s="49" t="s">
+        <v>390</v>
+      </c>
+      <c r="D43" s="49" t="s">
+        <v>391</v>
+      </c>
+      <c r="E43" s="49" t="s">
+        <v>392</v>
+      </c>
+      <c r="I43" s="18">
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <v>3</v>
+      </c>
+      <c r="L43" s="18">
+        <v>200</v>
+      </c>
+      <c r="M43">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B44" s="49">
+        <v>1</v>
+      </c>
+      <c r="C44" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="D44" s="49" t="s">
+        <v>391</v>
+      </c>
+      <c r="E44" s="49" t="s">
+        <v>392</v>
+      </c>
+      <c r="I44" s="18">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <v>5</v>
+      </c>
+      <c r="M44">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B45" s="49">
+        <v>1</v>
+      </c>
+      <c r="C45" s="49" t="s">
+        <v>393</v>
+      </c>
+      <c r="D45" s="49" t="s">
+        <v>394</v>
+      </c>
+      <c r="E45" s="49"/>
+      <c r="I45" s="18">
+        <v>2</v>
+      </c>
+      <c r="J45">
+        <v>6</v>
+      </c>
+      <c r="M45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B46" s="49">
+        <v>2</v>
+      </c>
+      <c r="C46" s="49" t="s">
+        <v>390</v>
+      </c>
+      <c r="D46" s="49" t="s">
+        <v>394</v>
+      </c>
+      <c r="E46" s="49" t="s">
+        <v>392</v>
+      </c>
+      <c r="I46" s="18">
+        <v>2</v>
+      </c>
+      <c r="J46">
+        <v>9</v>
+      </c>
+      <c r="M46">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B47" s="49">
+        <v>2</v>
+      </c>
+      <c r="C47" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="D47" s="49" t="s">
+        <v>395</v>
+      </c>
+      <c r="E47" s="49" t="s">
+        <v>392</v>
+      </c>
+      <c r="I47" s="18">
+        <v>2</v>
+      </c>
+      <c r="J47">
+        <v>10</v>
+      </c>
+      <c r="M47">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B48" s="49">
+        <v>2</v>
+      </c>
+      <c r="C48" s="49" t="s">
+        <v>393</v>
+      </c>
+      <c r="D48" s="49" t="s">
+        <v>396</v>
+      </c>
+      <c r="E48" s="49"/>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="49">
+        <v>2</v>
+      </c>
+      <c r="C49" s="49" t="s">
+        <v>397</v>
+      </c>
+      <c r="D49" s="49" t="s">
+        <v>396</v>
+      </c>
+      <c r="E49" s="49"/>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="49"/>
+      <c r="C50" s="49"/>
+      <c r="D50" s="49"/>
+      <c r="E50" s="49"/>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B51" s="49"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="49"/>
+      <c r="E51" s="49"/>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52" s="49"/>
+      <c r="C52" s="49"/>
+      <c r="D52" s="49"/>
+      <c r="E52" s="49"/>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53" s="49"/>
+      <c r="C53" s="49"/>
+      <c r="D53" s="49"/>
+      <c r="E53" s="49"/>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54" s="49"/>
+      <c r="C54" s="49"/>
+      <c r="D54" s="49"/>
+      <c r="E54" s="14" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E55" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E56" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E58" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E59" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E61" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E62" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E63" t="s">
+        <v>405</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="M26:N26"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="K33" r:id="rId1" xr:uid="{3184DF22-B205-4948-8FDE-2F70E6D5D4D6}"/>
+    <hyperlink ref="K34:K35" r:id="rId2" display="file://img01" xr:uid="{15B6963A-E21A-48A2-86C9-0BE507527FAE}"/>
+    <hyperlink ref="K34" r:id="rId3" xr:uid="{5048098E-8DF6-49DA-BAFD-EF2EB416602F}"/>
+    <hyperlink ref="K35" r:id="rId4" xr:uid="{648EA557-C8E8-4DA5-85F5-F68FEFA86D1C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId5"/>
+  <drawing r:id="rId6"/>
+  <legacyDrawing r:id="rId7"/>
 </worksheet>
 </file>